--- a/src/data/FORMATO_EDICION_PRODUCTOS_Masivos.xlsx
+++ b/src/data/FORMATO_EDICION_PRODUCTOS_Masivos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-I\EXCELS\actualizacion masiva\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33704681-AB9A-4EE4-83B6-FCB244F3362B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A97AF12-92B1-4E71-B022-04828DEC06E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33705" yWindow="0" windowWidth="24000" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2796" yWindow="0" windowWidth="10620" windowHeight="12384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTOS" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
   <si>
-    <t>DESCRIPCION</t>
-  </si>
-  <si>
     <t>MARCA</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>Tornillo para concreto HUS3 M8 x 100 estricto gravado-5 MASIVO</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
   </si>
 </sst>
 </file>
@@ -1023,72 +1023,72 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
         <v>118</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>119</v>
       </c>
-      <c r="E2" t="s">
-        <v>120</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" s="14">
         <v>98.735399999999998</v>
@@ -1105,31 +1105,31 @@
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>119</v>
       </c>
-      <c r="E3" t="s">
-        <v>120</v>
-      </c>
       <c r="F3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" s="14">
         <v>193.6054</v>
@@ -1146,31 +1146,31 @@
     </row>
     <row r="4" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="s">
         <v>118</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>119</v>
       </c>
-      <c r="E4" t="s">
-        <v>120</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J4" s="14">
         <v>79.543300000000002</v>
@@ -1187,31 +1187,31 @@
     </row>
     <row r="5" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
         <v>118</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>119</v>
       </c>
-      <c r="E5" t="s">
-        <v>120</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="14">
         <v>131.87190000000001</v>
@@ -1228,31 +1228,31 @@
     </row>
     <row r="6" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
         <v>118</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>119</v>
       </c>
-      <c r="E6" t="s">
-        <v>120</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>20</v>
-      </c>
       <c r="I6" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="14">
         <v>51.205100000000002</v>
@@ -3854,542 +3854,542 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B117" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B123" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
